--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hema.ananthan\eclipse-workspace\com.ggproduct.automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{6207B053-7F4C-4657-B23D-C0FD37C7A2B3}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{FF7D26D9-4A0A-48FD-91BD-47897E933563}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6960" activeTab="1" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -101,6 +101,15 @@
   </si>
   <si>
     <t>Automation application qualifications</t>
+  </si>
+  <si>
+    <t>CheckBox</t>
+  </si>
+  <si>
+    <t>Acknowledgment4__c</t>
+  </si>
+  <si>
+    <t>Checked</t>
   </si>
 </sst>
 </file>
@@ -515,7 +524,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A097844-34E4-4BE1-AA5B-8A6518D2ECB3}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="11.6328125" customWidth="1"/>
@@ -553,30 +562,30 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -587,10 +596,10 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -601,9 +610,23 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
         <v>23</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D7" t="s">
         <v>24</v>
       </c>
     </row>

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hema.ananthan\eclipse-workspace\com.ggproduct.automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{FF7D26D9-4A0A-48FD-91BD-47897E933563}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{AC1BB420-100B-4E65-BE81-93A25E4CD039}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6960" activeTab="1" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6960" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -49,9 +49,6 @@
     <t>Title__c</t>
   </si>
   <si>
-    <t>Automation Announcement Application</t>
-  </si>
-  <si>
     <t>Lookup</t>
   </si>
   <si>
@@ -67,18 +64,12 @@
     <t>RichText</t>
   </si>
   <si>
-    <t>ProposalDescription__c</t>
-  </si>
-  <si>
     <t>Automation application Project abstract</t>
   </si>
   <si>
     <t>Justification__c</t>
   </si>
   <si>
-    <t>Financials</t>
-  </si>
-  <si>
     <t>Automation application justification for project cost</t>
   </si>
   <si>
@@ -110,6 +101,15 @@
   </si>
   <si>
     <t>Checked</t>
+  </si>
+  <si>
+    <t>ProjectAbstract__c</t>
+  </si>
+  <si>
+    <t>Budget</t>
+  </si>
+  <si>
+    <t>Automation Announcement for Application Intake Application</t>
   </si>
 </sst>
 </file>
@@ -468,14 +468,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B87285-F8C8-4985-8D64-B234A73C3C3A}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="10.81640625" customWidth="1"/>
-    <col min="3" max="3" width="22.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" customWidth="1"/>
+    <col min="3" max="3" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -489,7 +489,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -500,21 +500,21 @@
         <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>9</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -525,14 +525,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A097844-34E4-4BE1-AA5B-8A6518D2ECB3}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11.6328125" customWidth="1"/>
-    <col min="3" max="3" width="23.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="44.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" customWidth="1"/>
+    <col min="3" max="3" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="44.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -546,91 +546,92 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
         <v>13</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
         <v>11</v>
       </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="C5" t="s">
         <v>16</v>
       </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>15</v>
       </c>
-      <c r="D4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
         <v>18</v>
       </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="D6" t="s">
         <v>19</v>
       </c>
-      <c r="D5" t="s">
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="D7" t="s">
         <v>21</v>
-      </c>
-      <c r="D6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hema.ananthan\eclipse-workspace\com.ggproduct.automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{AC1BB420-100B-4E65-BE81-93A25E4CD039}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{22987190-30D3-43F8-B330-AA79693E563A}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6960" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
@@ -109,7 +109,7 @@
     <t>Budget</t>
   </si>
   <si>
-    <t>Automation Announcement for Application Intake Application</t>
+    <t>Automation App Dec10</t>
   </si>
 </sst>
 </file>
@@ -468,14 +468,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B87285-F8C8-4985-8D64-B234A73C3C3A}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10.85546875" customWidth="1"/>
-    <col min="3" max="3" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="37.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.88671875" customWidth="1"/>
+    <col min="3" max="3" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -489,7 +489,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -503,7 +503,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -525,14 +525,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A097844-34E4-4BE1-AA5B-8A6518D2ECB3}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="11.5703125" customWidth="1"/>
-    <col min="3" max="3" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="44.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" customWidth="1"/>
+    <col min="3" max="3" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="44.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -546,7 +546,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -560,7 +560,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -574,7 +574,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -588,7 +588,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -602,7 +602,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -616,7 +616,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>15</v>
       </c>

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hema.ananthan\eclipse-workspace\com.ggproduct.automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{22987190-30D3-43F8-B330-AA79693E563A}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{16D27CFF-5A9A-404E-9561-0DA10E91A7A1}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6960" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6960" activeTab="2" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
-    <sheet name="Edition" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
+    <sheet name="Edition" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -467,53 +468,43 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B87285-F8C8-4985-8D64-B234A73C3C3A}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10.88671875" customWidth="1"/>
-    <col min="3" max="3" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="37.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
         <v>9</v>
       </c>
     </row>
@@ -523,110 +514,146 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A097844-34E4-4BE1-AA5B-8A6518D2ECB3}">
-  <dimension ref="A1:D7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8676E538-BD44-4E88-B93C-585B884C6D39}">
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="10.88671875" customWidth="1"/>
     <col min="2" max="2" width="11.5546875" customWidth="1"/>
-    <col min="3" max="3" width="23.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="44.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A097844-34E4-4BE1-AA5B-8A6518D2ECB3}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" t="s">
         <v>21</v>
       </c>
     </row>

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hema.ananthan\eclipse-workspace\com.ggproduct.automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{16D27CFF-5A9A-404E-9561-0DA10E91A7A1}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{DFCFC4AD-4A61-4930-8CDB-0A749D2C187D}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6960" activeTab="2" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="29">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -110,7 +110,10 @@
     <t>Budget</t>
   </si>
   <si>
-    <t>Automation App Dec10</t>
+    <t>Automation App Dec25</t>
+  </si>
+  <si>
+    <t>GranteeProgramincome__c</t>
   </si>
 </sst>
 </file>
@@ -573,7 +576,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A097844-34E4-4BE1-AA5B-8A6518D2ECB3}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
@@ -615,24 +618,24 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
+        <v>28</v>
+      </c>
+      <c r="C4">
+        <v>10000</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -640,10 +643,10 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -651,9 +654,20 @@
         <v>15</v>
       </c>
       <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
         <v>20</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C8" t="s">
         <v>21</v>
       </c>
     </row>

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="19126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hema.ananthan\eclipse-workspace\com.ggproduct.automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{DFCFC4AD-4A61-4930-8CDB-0A749D2C187D}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FE235D4-126D-4186-9247-B5F04F95CF1D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6960" activeTab="2" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6960" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -110,10 +110,10 @@
     <t>Budget</t>
   </si>
   <si>
-    <t>Automation App Dec25</t>
-  </si>
-  <si>
     <t>GranteeProgramincome__c</t>
+  </si>
+  <si>
+    <t>Automation App Jan10</t>
   </si>
 </sst>
 </file>
@@ -497,7 +497,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -621,7 +621,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C4">
         <v>10000</v>

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hema.ananthan\eclipse-workspace\com.ggproduct.automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FE235D4-126D-4186-9247-B5F04F95CF1D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5339CF52-BA3B-4467-A6B8-52523E9679F9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6960" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6960" activeTab="2" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
-    <sheet name="Edition" sheetId="2" r:id="rId3"/>
+    <sheet name="Form Fields 1" sheetId="4" r:id="rId2"/>
+    <sheet name="Form Fields 2" sheetId="5" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId4"/>
+    <sheet name="Edition" sheetId="2" r:id="rId5"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="45">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -113,7 +115,55 @@
     <t>GranteeProgramincome__c</t>
   </si>
   <si>
-    <t>Automation App Jan10</t>
+    <t>Automation App Jan16</t>
+  </si>
+  <si>
+    <t>SignedBy__c</t>
+  </si>
+  <si>
+    <t>SubmittedOnForm__c</t>
+  </si>
+  <si>
+    <t>Question1__c</t>
+  </si>
+  <si>
+    <t>Describe the activities and/or services to be provided</t>
+  </si>
+  <si>
+    <t>Question2__c</t>
+  </si>
+  <si>
+    <t>Describe the methodologies that will be used to complete activities/provide services</t>
+  </si>
+  <si>
+    <t>Question3__c</t>
+  </si>
+  <si>
+    <t>Describe how the project will be completed within the required 24-month timeline.</t>
+  </si>
+  <si>
+    <t>Question4__c</t>
+  </si>
+  <si>
+    <t>Question5__c</t>
+  </si>
+  <si>
+    <t>Question6__c</t>
+  </si>
+  <si>
+    <t>Question7__c</t>
+  </si>
+  <si>
+    <t>Question8__c</t>
+  </si>
+  <si>
+    <t>Question9__c</t>
+  </si>
+  <si>
+    <t>Question10__c</t>
+  </si>
+  <si>
+    <t>Question11__c</t>
   </si>
 </sst>
 </file>
@@ -474,7 +524,7 @@
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="37.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -517,6 +567,200 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2428A64E-9297-4AA1-BA48-EB8E69A06CF3}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78E5D97A-D013-4183-BB17-5426A6B81276}">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="76.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8676E538-BD44-4E88-B93C-585B884C6D39}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -574,7 +818,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A097844-34E4-4BE1-AA5B-8A6518D2ECB3}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hema.ananthan\eclipse-workspace\com.ggproduct.automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5339CF52-BA3B-4467-A6B8-52523E9679F9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0469B3E8-8273-4809-9158-C2D207D1955E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6960" activeTab="2" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6960" activeTab="4" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -115,9 +115,6 @@
     <t>GranteeProgramincome__c</t>
   </si>
   <si>
-    <t>Automation App Jan16</t>
-  </si>
-  <si>
     <t>SignedBy__c</t>
   </si>
   <si>
@@ -164,6 +161,9 @@
   </si>
   <si>
     <t>Question11__c</t>
+  </si>
+  <si>
+    <t>Automation App Jan19</t>
   </si>
 </sst>
 </file>
@@ -547,12 +547,12 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
@@ -591,7 +591,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
         <v>9</v>
@@ -602,7 +602,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -638,10 +638,10 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s">
         <v>31</v>
-      </c>
-      <c r="C2" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -649,10 +649,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
         <v>33</v>
-      </c>
-      <c r="C3" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -660,10 +660,10 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" t="s">
         <v>35</v>
-      </c>
-      <c r="C4" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -671,10 +671,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -682,10 +682,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -693,10 +693,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -704,10 +704,10 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -715,10 +715,10 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -726,10 +726,10 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -737,10 +737,10 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -748,10 +748,10 @@
         <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hema.ananthan\eclipse-workspace\com.ggproduct.automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0469B3E8-8273-4809-9158-C2D207D1955E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6ADB739-2F5F-4A6C-8F5C-BC6D032048AF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6960" activeTab="4" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6960" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -163,7 +163,7 @@
     <t>Question11__c</t>
   </si>
   <si>
-    <t>Automation App Jan19</t>
+    <t>Automation App Jan19 Vi</t>
   </si>
 </sst>
 </file>

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hema.ananthan\eclipse-workspace\com.ggproduct.automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6ADB739-2F5F-4A6C-8F5C-BC6D032048AF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A50E89B-B540-440C-AB7E-61E209630A35}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6960" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
@@ -163,7 +163,7 @@
     <t>Question11__c</t>
   </si>
   <si>
-    <t>Automation App Jan19 Vi</t>
+    <t>Automation Application Regression</t>
   </si>
 </sst>
 </file>

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hema.ananthan\eclipse-workspace\com.ggproduct.automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A50E89B-B540-440C-AB7E-61E209630A35}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{301F88E5-7E7B-4F09-8CEB-628A9F14A55D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6960" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
@@ -522,13 +522,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B87285-F8C8-4985-8D64-B234A73C3C3A}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="23.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -539,7 +539,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -550,7 +550,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -569,13 +569,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2428A64E-9297-4AA1-BA48-EB8E69A06CF3}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.5546875" customWidth="1"/>
+    <col min="3" max="3" width="23.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -586,7 +586,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -597,7 +597,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -616,13 +616,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78E5D97A-D013-4183-BB17-5426A6B81276}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="76.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="76.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -633,7 +633,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -644,7 +644,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -655,7 +655,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -666,7 +666,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -677,7 +677,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -688,7 +688,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -699,7 +699,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -710,7 +710,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -721,7 +721,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -732,7 +732,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -743,7 +743,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -763,13 +763,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8676E538-BD44-4E88-B93C-585B884C6D39}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" customWidth="1"/>
-    <col min="2" max="2" width="11.5546875" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -777,7 +777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -785,7 +785,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -793,22 +793,22 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>11</v>
       </c>
@@ -821,13 +821,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A097844-34E4-4BE1-AA5B-8A6518D2ECB3}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -838,7 +838,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -849,7 +849,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -860,7 +860,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -871,7 +871,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -882,7 +882,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -893,7 +893,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -904,7 +904,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>15</v>
       </c>

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hema.ananthan\eclipse-workspace\com.ggproduct.automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{301F88E5-7E7B-4F09-8CEB-628A9F14A55D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A68177B6-0150-4CF9-A661-509C9673C490}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6960" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -163,7 +163,7 @@
     <t>Question11__c</t>
   </si>
   <si>
-    <t>Automation Application Regression</t>
+    <t xml:space="preserve">Automation Application </t>
   </si>
 </sst>
 </file>
@@ -522,13 +522,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B87285-F8C8-4985-8D64-B234A73C3C3A}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -539,7 +539,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -550,7 +550,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -569,13 +569,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2428A64E-9297-4AA1-BA48-EB8E69A06CF3}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.5703125" customWidth="1"/>
+    <col min="3" max="3" width="23.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -586,7 +586,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -597,7 +597,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -616,13 +616,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78E5D97A-D013-4183-BB17-5426A6B81276}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="76.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="76.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -633,7 +633,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -644,7 +644,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -655,7 +655,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -666,7 +666,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -677,7 +677,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -688,7 +688,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -699,7 +699,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -710,7 +710,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -721,7 +721,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -732,7 +732,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -743,7 +743,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -763,13 +763,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8676E538-BD44-4E88-B93C-585B884C6D39}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" customWidth="1"/>
+    <col min="1" max="1" width="10.88671875" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -777,7 +777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -785,7 +785,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -793,22 +793,22 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>11</v>
       </c>
@@ -821,13 +821,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A097844-34E4-4BE1-AA5B-8A6518D2ECB3}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -838,7 +838,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -849,7 +849,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -860,7 +860,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -871,7 +871,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -882,7 +882,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -893,7 +893,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -904,7 +904,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>15</v>
       </c>

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A68177B6-0150-4CF9-A661-509C9673C490}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD1E58D-1482-46C8-B545-812AF803F6B5}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="37">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -73,97 +73,73 @@
     <t>Justification__c</t>
   </si>
   <si>
-    <t>Automation application justification for project cost</t>
-  </si>
-  <si>
-    <t>Proposal</t>
-  </si>
-  <si>
-    <t>ApproachMethodology__c</t>
-  </si>
-  <si>
-    <t>Automation application approach methodology</t>
-  </si>
-  <si>
-    <t>Capacity__c</t>
-  </si>
-  <si>
-    <t>Automation application capacity</t>
-  </si>
-  <si>
-    <t>Qualifications__c</t>
-  </si>
-  <si>
-    <t>Automation application qualifications</t>
-  </si>
-  <si>
     <t>CheckBox</t>
   </si>
   <si>
+    <t>Checked</t>
+  </si>
+  <si>
+    <t>ProjectAbstract__c</t>
+  </si>
+  <si>
+    <t>Budget</t>
+  </si>
+  <si>
+    <t>SubmittedOnForm__c</t>
+  </si>
+  <si>
+    <t>Question1__c</t>
+  </si>
+  <si>
+    <t>Describe the activities and/or services to be provided</t>
+  </si>
+  <si>
+    <t>Question2__c</t>
+  </si>
+  <si>
+    <t>Describe the methodologies that will be used to complete activities/provide services</t>
+  </si>
+  <si>
+    <t>Question3__c</t>
+  </si>
+  <si>
+    <t>Describe how the project will be completed within the required 24-month timeline.</t>
+  </si>
+  <si>
+    <t>Question4__c</t>
+  </si>
+  <si>
+    <t>Question5__c</t>
+  </si>
+  <si>
+    <t>Question6__c</t>
+  </si>
+  <si>
+    <t>Question7__c</t>
+  </si>
+  <si>
+    <t>Question8__c</t>
+  </si>
+  <si>
+    <t>Question9__c</t>
+  </si>
+  <si>
+    <t>Question10__c</t>
+  </si>
+  <si>
+    <t>Question11__c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Application </t>
+  </si>
+  <si>
+    <t>Justified</t>
+  </si>
+  <si>
+    <t>GranteeProgramincome__c</t>
+  </si>
+  <si>
     <t>Acknowledgment4__c</t>
-  </si>
-  <si>
-    <t>Checked</t>
-  </si>
-  <si>
-    <t>ProjectAbstract__c</t>
-  </si>
-  <si>
-    <t>Budget</t>
-  </si>
-  <si>
-    <t>GranteeProgramincome__c</t>
-  </si>
-  <si>
-    <t>SignedBy__c</t>
-  </si>
-  <si>
-    <t>SubmittedOnForm__c</t>
-  </si>
-  <si>
-    <t>Question1__c</t>
-  </si>
-  <si>
-    <t>Describe the activities and/or services to be provided</t>
-  </si>
-  <si>
-    <t>Question2__c</t>
-  </si>
-  <si>
-    <t>Describe the methodologies that will be used to complete activities/provide services</t>
-  </si>
-  <si>
-    <t>Question3__c</t>
-  </si>
-  <si>
-    <t>Describe how the project will be completed within the required 24-month timeline.</t>
-  </si>
-  <si>
-    <t>Question4__c</t>
-  </si>
-  <si>
-    <t>Question5__c</t>
-  </si>
-  <si>
-    <t>Question6__c</t>
-  </si>
-  <si>
-    <t>Question7__c</t>
-  </si>
-  <si>
-    <t>Question8__c</t>
-  </si>
-  <si>
-    <t>Question9__c</t>
-  </si>
-  <si>
-    <t>Question10__c</t>
-  </si>
-  <si>
-    <t>Question11__c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Application </t>
   </si>
 </sst>
 </file>
@@ -547,7 +523,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -568,7 +544,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2428A64E-9297-4AA1-BA48-EB8E69A06CF3}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
@@ -591,20 +567,9 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3">
+        <v>18</v>
+      </c>
+      <c r="C2">
         <v>0</v>
       </c>
     </row>
@@ -638,10 +603,10 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -649,10 +614,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -660,10 +625,10 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -671,10 +636,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -682,10 +647,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -693,10 +658,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -704,10 +669,10 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -715,10 +680,10 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -726,10 +691,10 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -737,10 +702,10 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -748,10 +713,10 @@
         <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -790,7 +755,7 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -820,7 +785,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A097844-34E4-4BE1-AA5B-8A6518D2ECB3}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
@@ -843,10 +808,10 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" t="s">
-        <v>12</v>
+        <v>35</v>
+      </c>
+      <c r="C2">
+        <v>10000</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -854,10 +819,10 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -865,54 +830,21 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4">
-        <v>10000</v>
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD1E58D-1482-46C8-B545-812AF803F6B5}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C11F11E-760A-4633-BE25-A474D56C1CE7}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="38">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -130,9 +130,6 @@
     <t>Question11__c</t>
   </si>
   <si>
-    <t xml:space="preserve">Automation Application </t>
-  </si>
-  <si>
     <t>Justified</t>
   </si>
   <si>
@@ -140,6 +137,12 @@
   </si>
   <si>
     <t>Acknowledgment4__c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Permanent Automation Application </t>
+  </si>
+  <si>
+    <t>AppplicationSubmitted__c</t>
   </si>
 </sst>
 </file>
@@ -497,7 +500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B87285-F8C8-4985-8D64-B234A73C3C3A}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
@@ -523,18 +526,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -544,7 +536,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2428A64E-9297-4AA1-BA48-EB8E69A06CF3}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
@@ -573,8 +565,20 @@
         <v>0</v>
       </c>
     </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -727,7 +731,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8676E538-BD44-4E88-B93C-585B884C6D39}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.88671875" customWidth="1"/>
@@ -776,6 +780,17 @@
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -808,10 +823,10 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2">
-        <v>10000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -819,7 +834,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C3" t="s">
         <v>15</v>
@@ -844,7 +859,7 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C11F11E-760A-4633-BE25-A474D56C1CE7}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D5ABD31-B9E9-4AD1-B732-B1BC8FCD92C9}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="4584" yWindow="3096" windowWidth="17280" windowHeight="8964" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -139,10 +139,10 @@
     <t>Acknowledgment4__c</t>
   </si>
   <si>
-    <t xml:space="preserve">Permanent Automation Application </t>
-  </si>
-  <si>
     <t>AppplicationSubmitted__c</t>
+  </si>
+  <si>
+    <t>Execution Announcement for Automation</t>
   </si>
 </sst>
 </file>
@@ -526,7 +526,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -570,7 +570,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -1,23 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21601"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D5ABD31-B9E9-4AD1-B732-B1BC8FCD92C9}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E3D6BC2-EE05-4389-84A7-ADD08AE6C80B}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4584" yWindow="3096" windowWidth="17280" windowHeight="8964" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="5" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
-    <sheet name="Creation" sheetId="1" r:id="rId1"/>
-    <sheet name="Form Fields 1" sheetId="4" r:id="rId2"/>
-    <sheet name="Form Fields 2" sheetId="5" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId4"/>
-    <sheet name="Edition" sheetId="2" r:id="rId5"/>
+    <sheet name="CreationPA" sheetId="6" r:id="rId1"/>
+    <sheet name="Pre-Application Modal" sheetId="7" r:id="rId2"/>
+    <sheet name="EditionPA" sheetId="8" r:id="rId3"/>
+    <sheet name="Creation" sheetId="1" r:id="rId4"/>
+    <sheet name="Form Fields 1" sheetId="4" r:id="rId5"/>
+    <sheet name="Edition" sheetId="2" r:id="rId6"/>
+    <sheet name="Form Fields 2" sheetId="5" r:id="rId7"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId8"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -29,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="79">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -133,26 +136,164 @@
     <t>Justified</t>
   </si>
   <si>
-    <t>GranteeProgramincome__c</t>
-  </si>
-  <si>
-    <t>Acknowledgment4__c</t>
-  </si>
-  <si>
     <t>AppplicationSubmitted__c</t>
   </si>
   <si>
     <t>Execution Announcement for Automation</t>
+  </si>
+  <si>
+    <t>IsMatchRequired__c</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>GranteeMatch__c</t>
+  </si>
+  <si>
+    <t>LaverageAllowed__c</t>
+  </si>
+  <si>
+    <t>IsProgramIncomeAnticipated__c</t>
+  </si>
+  <si>
+    <t>PreApplicationNeeded__c</t>
+  </si>
+  <si>
+    <t>WBSRequired__c</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>RiskAssessment_Required__c</t>
+  </si>
+  <si>
+    <t>FocusAreaRequired__c</t>
+  </si>
+  <si>
+    <t>IsGoalsRequired__c</t>
+  </si>
+  <si>
+    <t>KPIsRequired__c</t>
+  </si>
+  <si>
+    <t>AreExpensesBuildIUpLevel__c</t>
+  </si>
+  <si>
+    <t>IsAdvancePermitted__c</t>
+  </si>
+  <si>
+    <t>IsNegotiationsAllowed__c</t>
+  </si>
+  <si>
+    <t>AnnouncementDescription__c</t>
+  </si>
+  <si>
+    <t>Automation test description</t>
+  </si>
+  <si>
+    <t>MaxApplicationsAllowed__c</t>
+  </si>
+  <si>
+    <t>EligibleApplicantTypes__c</t>
+  </si>
+  <si>
+    <t>State governments;Independent school districts</t>
+  </si>
+  <si>
+    <t>ApplicationDueDate__c</t>
+  </si>
+  <si>
+    <t>QAAvailability__c</t>
+  </si>
+  <si>
+    <t>QSubmissionDeadline__c</t>
+  </si>
+  <si>
+    <t>AResponseDeadline__c</t>
+  </si>
+  <si>
+    <t>QAContactEmailAddress__c</t>
+  </si>
+  <si>
+    <t>hema.ananthan@reisystems.com</t>
+  </si>
+  <si>
+    <t>Financials</t>
+  </si>
+  <si>
+    <t>AwardFloor__c</t>
+  </si>
+  <si>
+    <t>AwardCeiling__c</t>
+  </si>
+  <si>
+    <t>EstimatedNumberOfAwards__c</t>
+  </si>
+  <si>
+    <t>TotalCommittedAmount__c</t>
+  </si>
+  <si>
+    <t>AnnouncementName__c</t>
+  </si>
+  <si>
+    <t>Automation Competitive Announcement for pre-application</t>
+  </si>
+  <si>
+    <t>Program__c</t>
+  </si>
+  <si>
+    <t>Automation Permanent Internal Program</t>
+  </si>
+  <si>
+    <t>Budget_Category_Package__c</t>
+  </si>
+  <si>
+    <t>Non-Construction</t>
+  </si>
+  <si>
+    <t>PROGRAMINCOME__c</t>
+  </si>
+  <si>
+    <t>ProjectGoal__c</t>
+  </si>
+  <si>
+    <t>ProjectBeneficiaries__c</t>
+  </si>
+  <si>
+    <t>Automation application Project  goal</t>
+  </si>
+  <si>
+    <t>Automation application Project beneficiaries</t>
+  </si>
+  <si>
+    <t>Agreement5__c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -175,10 +316,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -186,8 +328,11 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -499,6 +644,394 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC0ED488-2B1F-4F16-8235-EEBCD02879E6}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" customWidth="1"/>
+    <col min="3" max="3" width="43.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA4273BE-F829-4298-BC03-1F37623C37B1}">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A408404E-903C-4747-8B93-C5CB9A3B0B16}">
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13">
+        <v>100000</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C9" r:id="rId1" xr:uid="{45E7CAC3-36A2-4EED-BCFA-33A0CBFD3F8D}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B87285-F8C8-4985-8D64-B234A73C3C3A}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -526,7 +1059,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -534,7 +1067,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2428A64E-9297-4AA1-BA48-EB8E69A06CF3}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -570,7 +1103,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
@@ -582,7 +1115,99 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A097844-34E4-4BE1-AA5B-8A6518D2ECB3}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78E5D97A-D013-4183-BB17-5426A6B81276}">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -729,7 +1354,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8676E538-BD44-4E88-B93C-585B884C6D39}">
   <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -796,74 +1421,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A097844-34E4-4BE1-AA5B-8A6518D2ECB3}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
-</worksheet>
 </file>
--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace-Product-Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E3D6BC2-EE05-4389-84A7-ADD08AE6C80B}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8BB19A9-465C-4310-BA77-366133DF1336}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="5" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="5" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="CreationPA" sheetId="6" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="79">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -73,18 +73,12 @@
     <t>Automation application Project abstract</t>
   </si>
   <si>
-    <t>Justification__c</t>
-  </si>
-  <si>
     <t>CheckBox</t>
   </si>
   <si>
     <t>Checked</t>
   </si>
   <si>
-    <t>ProjectAbstract__c</t>
-  </si>
-  <si>
     <t>Budget</t>
   </si>
   <si>
@@ -253,29 +247,35 @@
     <t>Non-Construction</t>
   </si>
   <si>
-    <t>PROGRAMINCOME__c</t>
-  </si>
-  <si>
-    <t>ProjectGoal__c</t>
-  </si>
-  <si>
-    <t>ProjectBeneficiaries__c</t>
-  </si>
-  <si>
-    <t>Automation application Project  goal</t>
-  </si>
-  <si>
-    <t>Automation application Project beneficiaries</t>
-  </si>
-  <si>
-    <t>Agreement5__c</t>
+    <t>fieldProjectAbstract__c</t>
+  </si>
+  <si>
+    <t>fieldAcknowledgment4__c</t>
+  </si>
+  <si>
+    <t>fieldJustification__c</t>
+  </si>
+  <si>
+    <t>Proposal</t>
+  </si>
+  <si>
+    <t>fieldApproachMethodology__c</t>
+  </si>
+  <si>
+    <t>Automation Test Description</t>
+  </si>
+  <si>
+    <t>fieldCapacity__c</t>
+  </si>
+  <si>
+    <t>fieldQualifications__c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -297,6 +297,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF222222"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -320,7 +326,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -330,6 +336,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -646,14 +653,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC0ED488-2B1F-4F16-8235-EEBCD02879E6}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" customWidth="1"/>
-    <col min="3" max="3" width="43.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="3" max="3" width="43.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -664,37 +671,37 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
         <v>67</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C3" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
         <v>69</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C4" t="s">
         <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4" t="s">
-        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -705,13 +712,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA4273BE-F829-4298-BC03-1F37623C37B1}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -722,147 +729,147 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
         <v>36</v>
-      </c>
-      <c r="C2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>38</v>
       </c>
       <c r="C3">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
         <v>39</v>
       </c>
-      <c r="C4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
         <v>40</v>
       </c>
-      <c r="C5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C7" t="s">
         <v>41</v>
       </c>
-      <c r="C6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
         <v>42</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
         <v>44</v>
       </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" t="s">
         <v>45</v>
       </c>
-      <c r="C9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" t="s">
         <v>46</v>
       </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" t="s">
         <v>47</v>
       </c>
-      <c r="C11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="C13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" t="s">
         <v>48</v>
       </c>
-      <c r="C12" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" t="s">
-        <v>49</v>
-      </c>
-      <c r="C13" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" t="s">
-        <v>50</v>
-      </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -873,14 +880,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A408404E-903C-4747-8B93-C5CB9A3B0B16}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -891,133 +898,133 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C3">
         <v>200</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C5">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C7">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C8">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
       <c r="B9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>60</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="B10" t="s">
         <v>61</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>62</v>
-      </c>
-      <c r="B10" t="s">
-        <v>63</v>
       </c>
       <c r="C10">
         <v>1000</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" t="s">
         <v>62</v>
-      </c>
-      <c r="B11" t="s">
-        <v>64</v>
       </c>
       <c r="C11">
         <v>10000</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C12">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C13">
         <v>100000</v>
@@ -1034,13 +1041,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B87285-F8C8-4985-8D64-B234A73C3C3A}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1051,7 +1058,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1059,7 +1066,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1070,13 +1077,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2428A64E-9297-4AA1-BA48-EB8E69A06CF3}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.5546875" customWidth="1"/>
+    <col min="3" max="3" width="23.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1087,23 +1094,23 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
@@ -1117,14 +1124,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A097844-34E4-4BE1-AA5B-8A6518D2ECB3}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1135,88 +1142,94 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>74</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>75</v>
-      </c>
-      <c r="C4" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C5">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B7" t="s">
         <v>78</v>
       </c>
-      <c r="C6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
       <c r="C7" t="s">
-        <v>33</v>
-      </c>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B8" s="5"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B9" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78E5D97A-D013-4183-BB17-5426A6B81276}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="76.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="76.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1227,125 +1240,125 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
         <v>19</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
         <v>21</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
         <v>23</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
         <v>25</v>
       </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
         <v>26</v>
       </c>
-      <c r="C6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
         <v>27</v>
       </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
         <v>28</v>
       </c>
-      <c r="C8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" t="s">
         <v>29</v>
       </c>
-      <c r="C9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" t="s">
         <v>30</v>
       </c>
-      <c r="C10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" t="s">
-        <v>32</v>
-      </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1357,13 +1370,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8676E538-BD44-4E88-B93C-585B884C6D39}">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" customWidth="1"/>
-    <col min="2" max="2" width="11.5546875" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1371,7 +1384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1379,35 +1392,35 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>10</v>
       </c>

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace-Product-Automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8BB19A9-465C-4310-BA77-366133DF1336}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5987853C-84BC-435A-BCCD-A050C6C486EF}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="5" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
-    <sheet name="CreationPA" sheetId="6" r:id="rId1"/>
+    <sheet name="Editionpre-app" sheetId="6" r:id="rId1"/>
     <sheet name="Pre-Application Modal" sheetId="7" r:id="rId2"/>
     <sheet name="EditionPA" sheetId="8" r:id="rId3"/>
     <sheet name="Creation" sheetId="1" r:id="rId4"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="78">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -229,46 +229,43 @@
     <t>TotalCommittedAmount__c</t>
   </si>
   <si>
-    <t>AnnouncementName__c</t>
-  </si>
-  <si>
-    <t>Automation Competitive Announcement for pre-application</t>
-  </si>
-  <si>
-    <t>Program__c</t>
-  </si>
-  <si>
-    <t>Automation Permanent Internal Program</t>
-  </si>
-  <si>
-    <t>Budget_Category_Package__c</t>
-  </si>
-  <si>
-    <t>Non-Construction</t>
-  </si>
-  <si>
-    <t>fieldProjectAbstract__c</t>
-  </si>
-  <si>
-    <t>fieldAcknowledgment4__c</t>
-  </si>
-  <si>
-    <t>fieldJustification__c</t>
-  </si>
-  <si>
     <t>Proposal</t>
   </si>
   <si>
-    <t>fieldApproachMethodology__c</t>
-  </si>
-  <si>
     <t>Automation Test Description</t>
   </si>
   <si>
-    <t>fieldCapacity__c</t>
-  </si>
-  <si>
-    <t>fieldQualifications__c</t>
+    <t>ProjectAbstract__c</t>
+  </si>
+  <si>
+    <t>Acknowledgment4__c</t>
+  </si>
+  <si>
+    <t>Justification__c</t>
+  </si>
+  <si>
+    <t>ApproachMethodology__c</t>
+  </si>
+  <si>
+    <t>Capacity__c</t>
+  </si>
+  <si>
+    <t>Qualifications__c</t>
+  </si>
+  <si>
+    <t>ProjectGoal__c</t>
+  </si>
+  <si>
+    <t>ProjectBeneficiaries__c</t>
+  </si>
+  <si>
+    <t>Goal</t>
+  </si>
+  <si>
+    <t>benficianries</t>
+  </si>
+  <si>
+    <t>Agreement5__c</t>
   </si>
 </sst>
 </file>
@@ -292,14 +289,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <sz val="9"/>
+      <color rgb="FF222222"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="7"/>
       <color rgb="FF222222"/>
       <name val="Consolas"/>
       <family val="3"/>
@@ -652,15 +648,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC0ED488-2B1F-4F16-8235-EEBCD02879E6}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
-    <col min="3" max="3" width="43.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" customWidth="1"/>
+    <col min="3" max="3" width="43.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -671,54 +667,77 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
         <v>69</v>
       </c>
-      <c r="C4" t="s">
-        <v>70</v>
+      <c r="C6" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA4273BE-F829-4298-BC03-1F37623C37B1}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -729,7 +748,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -740,7 +759,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -751,7 +770,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -762,7 +781,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -773,7 +792,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -784,7 +803,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -795,7 +814,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -806,7 +825,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -817,7 +836,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -828,7 +847,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -839,7 +858,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -850,7 +869,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -861,7 +880,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -880,14 +899,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A408404E-903C-4747-8B93-C5CB9A3B0B16}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -898,7 +917,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -909,7 +928,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -920,7 +939,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -931,7 +950,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -942,7 +961,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -953,7 +972,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -964,7 +983,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -975,7 +994,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -986,7 +1005,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>60</v>
       </c>
@@ -997,7 +1016,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>60</v>
       </c>
@@ -1008,7 +1027,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>60</v>
       </c>
@@ -1019,7 +1038,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>60</v>
       </c>
@@ -1041,13 +1060,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B87285-F8C8-4985-8D64-B234A73C3C3A}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1058,7 +1077,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1077,13 +1096,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2428A64E-9297-4AA1-BA48-EB8E69A06CF3}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.5703125" customWidth="1"/>
+    <col min="3" max="3" width="23.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1094,7 +1113,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1105,7 +1124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1125,13 +1144,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A097844-34E4-4BE1-AA5B-8A6518D2ECB3}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1142,77 +1161,77 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="5"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="5"/>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B8" s="4"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B9" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1223,13 +1242,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78E5D97A-D013-4183-BB17-5426A6B81276}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="76.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="76.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1240,7 +1259,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1251,7 +1270,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1262,7 +1281,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1273,7 +1292,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1284,7 +1303,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1295,7 +1314,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -1306,7 +1325,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1317,7 +1336,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -1328,7 +1347,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -1339,7 +1358,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -1350,7 +1369,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -1370,13 +1389,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8676E538-BD44-4E88-B93C-585B884C6D39}">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" customWidth="1"/>
+    <col min="1" max="1" width="10.88671875" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1384,7 +1403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1392,7 +1411,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1400,27 +1419,27 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>10</v>
       </c>

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace-Product-Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5987853C-84BC-435A-BCCD-A050C6C486EF}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5779D913-74B9-41ED-86A0-6D5653069E19}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="5" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Editionpre-app" sheetId="6" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="80">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -238,21 +238,9 @@
     <t>ProjectAbstract__c</t>
   </si>
   <si>
-    <t>Acknowledgment4__c</t>
-  </si>
-  <si>
     <t>Justification__c</t>
   </si>
   <si>
-    <t>ApproachMethodology__c</t>
-  </si>
-  <si>
-    <t>Capacity__c</t>
-  </si>
-  <si>
-    <t>Qualifications__c</t>
-  </si>
-  <si>
     <t>ProjectGoal__c</t>
   </si>
   <si>
@@ -266,13 +254,31 @@
   </si>
   <si>
     <t>Agreement5__c</t>
+  </si>
+  <si>
+    <t>fieldAcknowledgment4__c</t>
+  </si>
+  <si>
+    <t>fieldProjectAbstract__c</t>
+  </si>
+  <si>
+    <t>fieldJustification__c</t>
+  </si>
+  <si>
+    <t>fieldApproachMethodology__c</t>
+  </si>
+  <si>
+    <t>fieldCapacity__c</t>
+  </si>
+  <si>
+    <t>fieldQualifications__c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -287,12 +293,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF222222"/>
-      <name val="Consolas"/>
-      <family val="3"/>
     </font>
     <font>
       <sz val="7"/>
@@ -322,7 +322,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -332,7 +332,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -649,14 +648,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC0ED488-2B1F-4F16-8235-EEBCD02879E6}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" customWidth="1"/>
-    <col min="3" max="3" width="43.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="3" max="3" width="43.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -667,7 +666,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -678,45 +677,45 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>74</v>
+      <c r="B3" s="4" t="s">
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>73</v>
-      </c>
-      <c r="C4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>77</v>
       </c>
       <c r="C5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
         <v>31</v>
@@ -731,13 +730,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA4273BE-F829-4298-BC03-1F37623C37B1}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -748,7 +747,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -759,7 +758,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -770,7 +769,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -781,7 +780,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -792,7 +791,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -803,7 +802,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -814,7 +813,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -825,7 +824,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -836,7 +835,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -847,7 +846,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -858,7 +857,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -869,7 +868,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -880,7 +879,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -899,14 +898,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A408404E-903C-4747-8B93-C5CB9A3B0B16}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -917,7 +916,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -928,7 +927,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -939,7 +938,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -950,7 +949,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -961,7 +960,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -972,7 +971,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -983,7 +982,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -994,7 +993,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1005,7 +1004,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>60</v>
       </c>
@@ -1016,7 +1015,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>60</v>
       </c>
@@ -1027,7 +1026,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>60</v>
       </c>
@@ -1038,7 +1037,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>60</v>
       </c>
@@ -1060,13 +1059,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B87285-F8C8-4985-8D64-B234A73C3C3A}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1077,7 +1076,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1096,13 +1095,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2428A64E-9297-4AA1-BA48-EB8E69A06CF3}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.5546875" customWidth="1"/>
+    <col min="3" max="3" width="23.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1113,7 +1112,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1124,7 +1123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1143,14 +1142,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A097844-34E4-4BE1-AA5B-8A6518D2ECB3}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1161,77 +1160,71 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>65</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>65</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>65</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B8" s="4"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B9" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1242,13 +1235,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78E5D97A-D013-4183-BB17-5426A6B81276}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="76.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="76.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1259,7 +1252,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1270,7 +1263,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1281,7 +1274,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1292,7 +1285,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1303,7 +1296,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1314,7 +1307,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -1325,7 +1318,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1336,7 +1329,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -1347,7 +1340,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -1358,7 +1351,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -1369,7 +1362,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -1389,13 +1382,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8676E538-BD44-4E88-B93C-585B884C6D39}">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" customWidth="1"/>
-    <col min="2" max="2" width="11.5546875" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1403,7 +1396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1411,7 +1404,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1419,27 +1412,27 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>10</v>
       </c>

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace-Product-Automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5779D913-74B9-41ED-86A0-6D5653069E19}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEFF77B2-2441-4E26-9686-C23F9D9CF2F3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="5" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Editionpre-app" sheetId="6" r:id="rId1"/>
-    <sheet name="Pre-Application Modal" sheetId="7" r:id="rId2"/>
-    <sheet name="EditionPA" sheetId="8" r:id="rId3"/>
-    <sheet name="Creation" sheetId="1" r:id="rId4"/>
-    <sheet name="Form Fields 1" sheetId="4" r:id="rId5"/>
-    <sheet name="Edition" sheetId="2" r:id="rId6"/>
-    <sheet name="Form Fields 2" sheetId="5" r:id="rId7"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId8"/>
+    <sheet name="EditionAcknowledge" sheetId="9" r:id="rId2"/>
+    <sheet name="Pre-Application Modal" sheetId="7" r:id="rId3"/>
+    <sheet name="EditionPA" sheetId="8" r:id="rId4"/>
+    <sheet name="Creation" sheetId="1" r:id="rId5"/>
+    <sheet name="Form Fields 1" sheetId="4" r:id="rId6"/>
+    <sheet name="Edition" sheetId="2" r:id="rId7"/>
+    <sheet name="Form Fields 2" sheetId="5" r:id="rId8"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId9"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="80">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -648,14 +649,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC0ED488-2B1F-4F16-8235-EEBCD02879E6}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
-    <col min="3" max="3" width="43.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" customWidth="1"/>
+    <col min="3" max="3" width="43.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -666,7 +667,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -677,7 +678,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -688,7 +689,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -699,7 +700,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -710,7 +711,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -728,15 +729,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA4273BE-F829-4298-BC03-1F37623C37B1}">
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{766848EE-2835-4541-A2DE-2EBCDE357668}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -747,147 +748,59 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="C3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="B5" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" t="s">
-        <v>47</v>
-      </c>
-      <c r="C13" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" t="s">
-        <v>48</v>
-      </c>
-      <c r="C14" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -896,16 +809,184 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA4273BE-F829-4298-BC03-1F37623C37B1}">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A408404E-903C-4747-8B93-C5CB9A3B0B16}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -916,7 +997,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -927,7 +1008,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -938,7 +1019,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -949,7 +1030,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -960,7 +1041,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -971,7 +1052,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -982,7 +1063,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -993,7 +1074,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1004,7 +1085,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>60</v>
       </c>
@@ -1015,7 +1096,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>60</v>
       </c>
@@ -1026,7 +1107,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>60</v>
       </c>
@@ -1037,7 +1118,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>60</v>
       </c>
@@ -1056,16 +1137,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B87285-F8C8-4985-8D64-B234A73C3C3A}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1076,7 +1157,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1092,16 +1173,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2428A64E-9297-4AA1-BA48-EB8E69A06CF3}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.5703125" customWidth="1"/>
+    <col min="3" max="3" width="23.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1112,7 +1193,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1123,7 +1204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1132,98 +1213,6 @@
       </c>
       <c r="C3" t="s">
         <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A097844-34E4-4BE1-AA5B-8A6518D2ECB3}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>65</v>
-      </c>
-      <c r="B7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C7" t="s">
-        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1233,15 +1222,107 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A097844-34E4-4BE1-AA5B-8A6518D2ECB3}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78E5D97A-D013-4183-BB17-5426A6B81276}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="76.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="76.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1252,7 +1333,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1263,7 +1344,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1274,7 +1355,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1285,7 +1366,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1296,7 +1377,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1307,7 +1388,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -1318,7 +1399,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1329,7 +1410,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -1340,7 +1421,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -1351,7 +1432,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -1362,7 +1443,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -1379,16 +1460,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8676E538-BD44-4E88-B93C-585B884C6D39}">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" customWidth="1"/>
+    <col min="1" max="1" width="10.88671875" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1396,7 +1477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1404,7 +1485,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1412,27 +1493,27 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>10</v>
       </c>

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEFF77B2-2441-4E26-9686-C23F9D9CF2F3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7249333F-2162-4D59-A5A5-99B060D44EE3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Editionpre-app" sheetId="6" r:id="rId1"/>
     <sheet name="EditionAcknowledge" sheetId="9" r:id="rId2"/>
-    <sheet name="Pre-Application Modal" sheetId="7" r:id="rId3"/>
-    <sheet name="EditionPA" sheetId="8" r:id="rId4"/>
-    <sheet name="Creation" sheetId="1" r:id="rId5"/>
-    <sheet name="Form Fields 1" sheetId="4" r:id="rId6"/>
-    <sheet name="Edition" sheetId="2" r:id="rId7"/>
-    <sheet name="Form Fields 2" sheetId="5" r:id="rId8"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId9"/>
+    <sheet name="AddressValues" sheetId="10" r:id="rId3"/>
+    <sheet name="Pre-Application Modal" sheetId="7" r:id="rId4"/>
+    <sheet name="EditionPA" sheetId="8" r:id="rId5"/>
+    <sheet name="Creation" sheetId="1" r:id="rId6"/>
+    <sheet name="Form Fields 1" sheetId="4" r:id="rId7"/>
+    <sheet name="Edition" sheetId="2" r:id="rId8"/>
+    <sheet name="Form Fields 2" sheetId="5" r:id="rId9"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId10"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="84">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -273,6 +274,18 @@
   </si>
   <si>
     <t>fieldQualifications__c</t>
+  </si>
+  <si>
+    <t>Sterling</t>
+  </si>
+  <si>
+    <t>Addressline1__c</t>
+  </si>
+  <si>
+    <t>city__c</t>
+  </si>
+  <si>
+    <t>Herndon</t>
   </si>
 </sst>
 </file>
@@ -728,6 +741,75 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8676E538-BD44-4E88-B93C-585B884C6D39}">
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.88671875" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{766848EE-2835-4541-A2DE-2EBCDE357668}">
   <dimension ref="A1:C6"/>
@@ -809,6 +891,54 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D16F34EE-937B-4D9C-AA9F-266997B4D30C}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA4273BE-F829-4298-BC03-1F37623C37B1}">
   <dimension ref="A1:C14"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -976,7 +1106,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A408404E-903C-4747-8B93-C5CB9A3B0B16}">
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1137,7 +1267,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B87285-F8C8-4985-8D64-B234A73C3C3A}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1173,7 +1303,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2428A64E-9297-4AA1-BA48-EB8E69A06CF3}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1221,7 +1351,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A097844-34E4-4BE1-AA5B-8A6518D2ECB3}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1313,7 +1443,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78E5D97A-D013-4183-BB17-5426A6B81276}">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1458,73 +1588,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8676E538-BD44-4E88-B93C-585B884C6D39}">
-  <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="10.88671875" customWidth="1"/>
-    <col min="2" max="2" width="11.5546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>10</v>
-      </c>
-      <c r="B21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" t="s">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10113"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jitendrapisal/rei/govgrants-product-automation/src/main/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7249333F-2162-4D59-A5A5-99B060D44EE3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09959F57-D600-2E4A-831D-215F6EF1B2DA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="0" yWindow="460" windowWidth="23260" windowHeight="12580" activeTab="2" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Editionpre-app" sheetId="6" r:id="rId1"/>
@@ -282,17 +282,17 @@
     <t>Addressline1__c</t>
   </si>
   <si>
-    <t>city__c</t>
-  </si>
-  <si>
     <t>Herndon</t>
+  </si>
+  <si>
+    <t>City__c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -313,6 +313,12 @@
       <color rgb="FF222222"/>
       <name val="Consolas"/>
       <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF222222"/>
+      <name val="Menlo"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -336,7 +342,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -346,6 +352,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -662,14 +669,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC0ED488-2B1F-4F16-8235-EEBCD02879E6}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.33203125" customWidth="1"/>
-    <col min="3" max="3" width="43.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -680,7 +687,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -691,7 +698,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -702,7 +709,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -713,7 +720,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -724,7 +731,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -744,13 +751,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8676E538-BD44-4E88-B93C-585B884C6D39}">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" customWidth="1"/>
-    <col min="2" max="2" width="11.5546875" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="2" max="2" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -758,7 +765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -766,7 +773,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -774,27 +781,27 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>10</v>
       </c>
@@ -813,13 +820,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{766848EE-2835-4541-A2DE-2EBCDE357668}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -830,7 +837,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -841,7 +848,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -852,7 +859,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>65</v>
       </c>
@@ -863,7 +870,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>65</v>
       </c>
@@ -874,7 +881,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>65</v>
       </c>
@@ -893,13 +900,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D16F34EE-937B-4D9C-AA9F-266997B4D30C}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -910,7 +917,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -921,15 +928,15 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" t="s">
         <v>82</v>
-      </c>
-      <c r="C3" t="s">
-        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -941,13 +948,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA4273BE-F829-4298-BC03-1F37623C37B1}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -958,7 +965,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -969,7 +976,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -980,7 +987,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -991,7 +998,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1002,7 +1009,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1013,7 +1020,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -1024,7 +1031,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1035,7 +1042,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -1046,7 +1053,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -1057,7 +1064,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -1068,7 +1075,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -1079,7 +1086,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -1090,7 +1097,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -1109,14 +1116,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A408404E-903C-4747-8B93-C5CB9A3B0B16}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1127,7 +1134,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1138,7 +1145,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1149,7 +1156,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1160,7 +1167,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1171,7 +1178,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1182,7 +1189,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -1193,7 +1200,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1204,7 +1211,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1215,7 +1222,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>60</v>
       </c>
@@ -1226,7 +1233,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>60</v>
       </c>
@@ -1237,7 +1244,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>60</v>
       </c>
@@ -1248,7 +1255,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>60</v>
       </c>
@@ -1270,13 +1277,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B87285-F8C8-4985-8D64-B234A73C3C3A}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1287,7 +1294,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1306,13 +1313,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2428A64E-9297-4AA1-BA48-EB8E69A06CF3}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.5546875" customWidth="1"/>
+    <col min="3" max="3" width="23.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1323,7 +1330,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1334,7 +1341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1354,13 +1361,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A097844-34E4-4BE1-AA5B-8A6518D2ECB3}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1371,7 +1378,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1382,7 +1389,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1393,7 +1400,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -1404,7 +1411,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>65</v>
       </c>
@@ -1415,7 +1422,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>65</v>
       </c>
@@ -1426,7 +1433,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>65</v>
       </c>
@@ -1446,13 +1453,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78E5D97A-D013-4183-BB17-5426A6B81276}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="76.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="76.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1463,7 +1470,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1474,7 +1481,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1485,7 +1492,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1496,7 +1503,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1507,7 +1514,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1518,7 +1525,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -1529,7 +1536,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1540,7 +1547,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -1551,7 +1558,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -1562,7 +1569,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -1573,7 +1580,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>4</v>
       </c>

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10113"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25128"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jitendrapisal/rei/govgrants-product-automation/src/main/resources/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09959F57-D600-2E4A-831D-215F6EF1B2DA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8075E0FA-F368-45F3-A6F6-1AFD783085DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="460" windowWidth="23260" windowHeight="12580" activeTab="2" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="7" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Editionpre-app" sheetId="6" r:id="rId1"/>
@@ -292,7 +292,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -669,14 +669,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC0ED488-2B1F-4F16-8235-EEBCD02879E6}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" customWidth="1"/>
-    <col min="3" max="3" width="43.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="3" max="3" width="43.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -687,7 +687,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -698,7 +698,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -709,7 +709,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -720,7 +720,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -731,7 +731,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -751,13 +751,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8676E538-BD44-4E88-B93C-585B884C6D39}">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" customWidth="1"/>
-    <col min="2" max="2" width="11.5" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -765,7 +765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -773,7 +773,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -781,27 +781,27 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2">
       <c r="B4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2">
       <c r="B5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2">
       <c r="B6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2">
       <c r="B7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>10</v>
       </c>
@@ -820,13 +820,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{766848EE-2835-4541-A2DE-2EBCDE357668}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="23.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -837,7 +837,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -848,7 +848,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -859,7 +859,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>65</v>
       </c>
@@ -870,7 +870,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>65</v>
       </c>
@@ -881,7 +881,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>65</v>
       </c>
@@ -900,13 +900,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D16F34EE-937B-4D9C-AA9F-266997B4D30C}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -917,7 +917,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -928,7 +928,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -948,13 +948,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA4273BE-F829-4298-BC03-1F37623C37B1}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -965,7 +965,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -976,7 +976,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -987,7 +987,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -998,7 +998,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1009,7 +1009,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -1031,7 +1031,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1042,7 +1042,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -1053,7 +1053,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -1064,7 +1064,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -1075,7 +1075,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -1086,7 +1086,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -1097,7 +1097,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -1116,14 +1116,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A408404E-903C-4747-8B93-C5CB9A3B0B16}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1134,7 +1134,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1145,7 +1145,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1156,7 +1156,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1167,7 +1167,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1178,7 +1178,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1189,7 +1189,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -1200,7 +1200,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1211,7 +1211,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1222,7 +1222,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>60</v>
       </c>
@@ -1233,7 +1233,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>60</v>
       </c>
@@ -1244,7 +1244,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>60</v>
       </c>
@@ -1255,7 +1255,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>60</v>
       </c>
@@ -1277,13 +1277,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B87285-F8C8-4985-8D64-B234A73C3C3A}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1294,7 +1294,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1313,13 +1313,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2428A64E-9297-4AA1-BA48-EB8E69A06CF3}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.5" customWidth="1"/>
+    <col min="3" max="3" width="23.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1330,7 +1330,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1341,7 +1341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1361,13 +1361,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A097844-34E4-4BE1-AA5B-8A6518D2ECB3}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="23.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1378,7 +1378,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1400,7 +1400,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -1411,7 +1411,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>65</v>
       </c>
@@ -1422,7 +1422,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>65</v>
       </c>
@@ -1433,7 +1433,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>65</v>
       </c>
@@ -1453,13 +1453,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78E5D97A-D013-4183-BB17-5426A6B81276}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="76.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="76.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1470,7 +1470,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1481,7 +1481,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1492,7 +1492,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1514,7 +1514,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1525,7 +1525,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -1536,7 +1536,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1547,7 +1547,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -1558,7 +1558,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -1569,7 +1569,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -1580,7 +1580,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>4</v>
       </c>
